--- a/outputs/FY2026-01-management-pack.xlsx
+++ b/outputs/FY2026-01-management-pack.xlsx
@@ -1029,7 +1029,7 @@
         <v>84180.67</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>70000</v>
+        <v>83337.82000000001</v>
       </c>
       <c r="E23" s="10">
         <f>C23-D23</f>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="H29" s="36" t="inlineStr">
         <is>
-          <t>January sticks +13,991; -42,490 materializes on the open months. -100,251 in Q1 if the accrual holds at 100% of target; each 10 points of company multiplier is roughly USD 10.4k a quarter in G&amp;A alone.</t>
+          <t>January sticks +13,991; -42,490 materializes on the open months. Not an overspend.</t>
         </is>
       </c>
       <c r="I29" s="36" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="H30" s="36" t="inlineStr">
         <is>
-          <t>January sticks +148,153; -74,064 materializes on the open months. +64,900 a month while the roster holds; +129,800 Feb+Mar.</t>
+          <t>January sticks +148,153; -74,064 materializes on the open months. Loaded rate USD 17,051 against USD 19,322 planned = +88,574 (roster loaded average USD 193,505 against the plan's USD 214,000); heads 39 against....</t>
         </is>
       </c>
       <c r="I30" s="36" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="H31" s="36" t="inlineStr">
         <is>
-          <t>January sticks -221,052. -177,000 Feb+Mar if the reservation recurs; -88,500 Jan already booked.</t>
+          <t>January sticks -221,052. CoreWeave reserved H200 training capacity USD 88,500, moved out of cost of revenue by ADJ-2026-01-003; the 6050 envelope of USD 26,318 was never....</t>
         </is>
       </c>
       <c r="I31" s="36" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="H32" s="36" t="inlineStr">
         <is>
-          <t>January sticks +59,315. +64,900 a month while the roster holds; +129,800 Feb+Mar.</t>
+          <t>January sticks +59,315. Loaded rate USD 17,051 against USD 19,322 planned = +88,574 (roster loaded average USD 193,505 against the plan's USD 214,000); heads 39 against....</t>
         </is>
       </c>
       <c r="I32" s="36" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="H33" s="36" t="inlineStr">
         <is>
-          <t>January sticks +46,139. +64,900 a month while the roster holds; +129,800 Feb+Mar.</t>
+          <t>January sticks +46,139. Loaded rate USD 17,051 against USD 19,322 planned = +88,574 (roster loaded average USD 193,505 against the plan's USD 214,000); heads 39 against....</t>
         </is>
       </c>
       <c r="I33" s="36" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="H34" s="36" t="inlineStr">
         <is>
-          <t>+71,084 materializes on the open months. Q1 favorable approx USD 255k.</t>
+          <t>+71,084 materializes on the open months. Loaded cost per head, not heads.</t>
         </is>
       </c>
       <c r="I34" s="36" t="inlineStr">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="H35" s="36" t="inlineStr">
         <is>
-          <t>+38,496 materializes on the open months. Q1 favorable approx USD 255k.</t>
+          <t>+38,496 materializes on the open months. Loaded cost per head, not heads.</t>
         </is>
       </c>
       <c r="I35" s="36" t="inlineStr">
@@ -7703,7 +7703,7 @@
       </c>
       <c r="H36" s="36" t="inlineStr">
         <is>
-          <t>+41,327 materializes on the open months. Q1 favorable approx USD 255k.</t>
+          <t>+41,327 materializes on the open months. Loaded cost per head, not heads.</t>
         </is>
       </c>
       <c r="I36" s="36" t="inlineStr">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="H37" s="36" t="inlineStr">
         <is>
-          <t>+8,492 materializes on the open months. Q1 favorable approx USD 255k.</t>
+          <t>+8,492 materializes on the open months. Loaded cost per head, not heads.</t>
         </is>
       </c>
       <c r="I37" s="36" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="H38" s="36" t="inlineStr">
         <is>
-          <t>+30,486 materializes on the open months. Q1 favorable approx USD 255k.</t>
+          <t>+30,486 materializes on the open months. Loaded cost per head, not heads.</t>
         </is>
       </c>
       <c r="I38" s="36" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="H39" s="36" t="inlineStr">
         <is>
-          <t>+33,646 materializes on the open months. Q1 favorable approx USD 255k.</t>
+          <t>+33,646 materializes on the open months. Loaded cost per head, not heads.</t>
         </is>
       </c>
       <c r="I39" s="36" t="inlineStr">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="H40" s="36" t="inlineStr">
         <is>
-          <t>+40,569 materializes on the open months. Q1 favorable approx USD 255k.</t>
+          <t>+40,569 materializes on the open months. Loaded cost per head, not heads.</t>
         </is>
       </c>
       <c r="I40" s="36" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="H41" s="36" t="inlineStr">
         <is>
-          <t>January sticks -4,361; -40,010 materializes on the open months. +29,912 in Q1 (Jan +36,559, Feb -3,324, Mar -3,324); nil for the full year.</t>
+          <t>January sticks -4,361; -40,010 materializes on the open months. Delaware franchise tax invoiced in full at USD 39,882 on 6 Jan and spread over the year it covers by ADJ-2026-01-010; the plan expensed the whole....</t>
         </is>
       </c>
       <c r="I41" s="36" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="H42" s="36" t="inlineStr">
         <is>
-          <t>-37,970 materializes on the open months. -23,106 in Q1 at the January rate; the account is -24,660 including Riviera Partners.</t>
+          <t>-37,970 materializes on the open months. The plan is the problem, not the month.</t>
         </is>
       </c>
       <c r="I42" s="36" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="H43" s="36" t="inlineStr">
         <is>
-          <t>January sticks -35,162; -25,627 materializes on the open months. -35,162 in Q1 (Jan -25,364, Feb -10,224, Mar +426), of which -19,400 is the non-recurring renewal accrual.</t>
+          <t>January sticks -35,162; -25,627 materializes on the open months. Two components.</t>
         </is>
       </c>
       <c r="I43" s="36" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H44" s="36" t="inlineStr">
         <is>
-          <t>-13,280 materializes on the open months. -100,251 in Q1 if the accrual holds at 100% of target; each 10 points of company multiplier is roughly USD 10.4k a quarter in G&amp;A alone.</t>
+          <t>-13,280 materializes on the open months. Not an overspend.</t>
         </is>
       </c>
       <c r="I44" s="36" t="inlineStr">
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>211200</v>
+        <v>242590.41</v>
       </c>
       <c r="D49" s="10" t="n">
         <v>0</v>
@@ -8424,7 +8424,7 @@
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>-47938.54</v>
+        <v>-48897.36</v>
       </c>
       <c r="H69" s="36" t="inlineStr">
         <is>
@@ -8480,165 +8480,165 @@
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>6030 R&amp;D - contractors / Thoughtbolt Engineering LLC</t>
+          <t>4020 Professional services revenue / (customer billing)</t>
         </is>
       </c>
       <c r="C73" s="10" t="n">
-        <v>-17221.02</v>
+        <v>4565.35</v>
       </c>
       <c r="H73" s="36" t="inlineStr">
         <is>
-          <t>Volume-driven. Invoiced hours USD 25,525.50 (in line with the December run rate of USD 24,310) plus a USD 16,200 accrual for January hours on TBE-0126 - the whole overrun is the accrual</t>
+          <t>Timing. Milestone delivery landed USD 4,565 ahead of the planned schedule on a line with a coefficient of variation of 0.503. Against the trailing 3-month average of USD 120,458 the month is down USD 23,892, which is calendar, not trend.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>4020 Professional services revenue / (customer billing)</t>
+          <t>7060 S&amp;M - software and tools / All other agreements (six vendors)</t>
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>4565.35</v>
+        <v>3684.07</v>
       </c>
       <c r="H74" s="36" t="inlineStr">
         <is>
-          <t>Timing. Milestone delivery landed USD 4,565 ahead of the planned schedule on a line with a coefficient of variation of 0.503. Against the trailing 3-month average of USD 120,458 the month is down USD 23,892, which is calendar, not trend.</t>
+          <t>Timing. Every non-Gong agreement in 7060 is favorable by exactly 9.55 percent - Clearscope, HubSpot, Salesforce, Sprout Social, Webflow and ZoomInfo, plus Chorus and Lucid above. A single identical percentage across eight independent contracts is a release-convention artifact, not eight separate savings. It offsets most of the Gong uplift at the account level (7060 total unfavorable only USD 832 against a Gong uplift of USD 6,156), which is exactly how a real cost increase gets hidden in an account subtotal.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>7060 S&amp;M - software and tools / All other agreements (six vendors)</t>
+          <t>6030 R&amp;D - contractors / Thoughtbolt Engineering LLC</t>
         </is>
       </c>
       <c r="C75" s="10" t="n">
-        <v>3684.07</v>
+        <v>-1021.02</v>
       </c>
       <c r="H75" s="36" t="inlineStr">
         <is>
-          <t>Timing. Every non-Gong agreement in 7060 is favorable by exactly 9.55 percent - Clearscope, HubSpot, Salesforce, Sprout Social, Webflow and ZoomInfo, plus Chorus and Lucid above. A single identical percentage across eight independent contracts is a release-convention artifact, not eight separate savings. It offsets most of the Gong uplift at the account level (7060 total unfavorable only USD 832 against a Gong uplift of USD 6,156), which is exactly how a real cost increase gets hidden in an account subtotal.</t>
+          <t>Volume-driven. Invoiced hours USD 25,525.50 (in line with the December run rate of USD 24,310) plus a USD 16,200 accrual for January hours on TBE-0126 - the whole overrun is the accrual</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>8050 G&amp;A - software and tools / Okta, Inc.</t>
+          <t>7050 S&amp;M - events and conferences / Freeman, Goldcast, Informa</t>
         </is>
       </c>
       <c r="C76" s="10" t="n">
-        <v>3141.29</v>
+        <v>672</v>
       </c>
       <c r="H76" s="36" t="inlineStr">
         <is>
-          <t>Accrual artifact. Not a saving. Every one of the eight prepaid-released G&amp;A subscriptions is favorable by exactly 40.97 percent - the release is 59.03 percent of contracted ACV/12 on all eight, to five decimal places. One common factor, so one common cause: the prepaid amortization schedule is releasing below the contracted rate. The agreement (SWA-0065) is a 12-month term at USD 92,000 with 0 percent uplift and the sole 8050 posting for this vendor is the prepaid release, so ACV/12 is the correct monthly charge. Licenses active 97 of 120. Under-release understates expense now and leaves a prepaid balance that will not extinguish at term end.</t>
+          <t>Timing. Calendar-driven, not a trend. The plan itself ramps across Q1 (Jan USD 8,400, Feb USD 11,760, Mar USD 26,880) because the named event calendar puts the Q1 event in March. Trailing three-month average of USD 21,467 is inflated by Q4-2025 events; the trend file flags the line bumpy (CoV 0.83) and says so. January is on the calendar and on plan.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>8050 G&amp;A - software and tools / Slack (Salesforce)</t>
+          <t>8050 G&amp;A - software and tools / Okta, Inc.</t>
         </is>
       </c>
       <c r="C77" s="10" t="n">
-        <v>2663.26</v>
+        <v>0</v>
       </c>
       <c r="H77" s="36" t="inlineStr">
         <is>
-          <t>Accrual artifact. Not a saving. Every one of the eight prepaid-released G&amp;A subscriptions is favorable by exactly 40.97 percent - the release is 59.03 percent of contracted ACV/12 on all eight, to five decimal places. One common factor, so one common cause: the prepaid amortization schedule is releasing below the contracted rate. The agreement (SWA-0069) is a 12-month term at USD 78,000 with 0 percent uplift and the sole 8050 posting for this vendor is the prepaid release, so ACV/12 is the correct monthly charge. Licenses active 143 of 180. Under-release understates expense now and leaves a prepaid balance that will not extinguish at term end.</t>
+          <t>Accrual artifact. Not a saving. Every one of the eight prepaid-released G&amp;A subscriptions is favorable by exactly 40.97 percent - the release is 59.03 percent of contracted ACV/12 on all eight, to five decimal places. One common factor, so one common cause: the prepaid amortization schedule is releasing below the contracted rate. The agreement (SWA-0065) is a 12-month term at USD 92,000 with 0 percent uplift and the sole 8050 posting for this vendor is the prepaid release, so ACV/12 is the correct monthly charge. Licenses active 97 of 120. Under-release understates expense now and leaves a prepaid balance that will not extinguish at term end.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>8050 G&amp;A - software and tools / CrowdStrike, Inc.</t>
+          <t>8050 G&amp;A - software and tools / Slack (Salesforce)</t>
         </is>
       </c>
       <c r="C78" s="10" t="n">
-        <v>2185.24</v>
+        <v>0</v>
       </c>
       <c r="H78" s="36" t="inlineStr">
         <is>
-          <t>Accrual artifact. Not a saving. Every one of the eight prepaid-released G&amp;A subscriptions is favorable by exactly 40.97 percent - the release is 59.03 percent of contracted ACV/12 on all eight, to five decimal places. One common factor, so one common cause: the prepaid amortization schedule is releasing below the contracted rate. The agreement (SWA-0067) is a 12-month term at USD 64,000 with 0 percent uplift and the sole 8050 posting for this vendor is the prepaid release, so ACV/12 is the correct monthly charge. Licenses active not seat-based. Under-release understates expense now and leaves a prepaid balance that will not extinguish at term end.</t>
+          <t>Accrual artifact. Not a saving. Every one of the eight prepaid-released G&amp;A subscriptions is favorable by exactly 40.97 percent - the release is 59.03 percent of contracted ACV/12 on all eight, to five decimal places. One common factor, so one common cause: the prepaid amortization schedule is releasing below the contracted rate. The agreement (SWA-0069) is a 12-month term at USD 78,000 with 0 percent uplift and the sole 8050 posting for this vendor is the prepaid release, so ACV/12 is the correct monthly charge. Licenses active 143 of 180. Under-release understates expense now and leaves a prepaid balance that will not extinguish at term end.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>8050 G&amp;A - software and tools / Vanta Inc.</t>
+          <t>8050 G&amp;A - software and tools / CrowdStrike, Inc.</t>
         </is>
       </c>
       <c r="C79" s="10" t="n">
-        <v>1297.49</v>
+        <v>0</v>
       </c>
       <c r="H79" s="36" t="inlineStr">
         <is>
-          <t>Accrual artifact. Not a saving. Every one of the eight prepaid-released G&amp;A subscriptions is favorable by exactly 40.97 percent - the release is 59.03 percent of contracted ACV/12 on all eight, to five decimal places. One common factor, so one common cause: the prepaid amortization schedule is releasing below the contracted rate. The agreement (SWA-0064) is a 12-month term at USD 38,000 with 0 percent uplift and the sole 8050 posting for this vendor is the prepaid release, so ACV/12 is the correct monthly charge. Licenses active not seat-based. Under-release understates expense now and leaves a prepaid balance that will not extinguish at term end.</t>
+          <t>Accrual artifact. Not a saving. Every one of the eight prepaid-released G&amp;A subscriptions is favorable by exactly 40.97 percent - the release is 59.03 percent of contracted ACV/12 on all eight, to five decimal places. One common factor, so one common cause: the prepaid amortization schedule is releasing below the contracted rate. The agreement (SWA-0067) is a 12-month term at USD 64,000 with 0 percent uplift and the sole 8050 posting for this vendor is the prepaid release, so ACV/12 is the correct monthly charge. Licenses active not seat-based. Under-release understates expense now and leaves a prepaid balance that will not extinguish at term end.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>8050 G&amp;A - software and tools / Zoom Communications</t>
+          <t>8050 G&amp;A - software and tools / Vanta Inc.</t>
         </is>
       </c>
       <c r="C80" s="10" t="n">
-        <v>1160.91</v>
+        <v>0</v>
       </c>
       <c r="H80" s="36" t="inlineStr">
         <is>
-          <t>Accrual artifact. Not a saving. Every one of the eight prepaid-released G&amp;A subscriptions is favorable by exactly 40.97 percent - the release is 59.03 percent of contracted ACV/12 on all eight, to five decimal places. One common factor, so one common cause: the prepaid amortization schedule is releasing below the contracted rate. The agreement (SWA-0071) is a 12-month term at USD 34,000 with 0 percent uplift and the sole 8050 posting for this vendor is the prepaid release, so ACV/12 is the correct monthly charge. Licenses active 31 of 45. Under-release understates expense now and leaves a prepaid balance that will not extinguish at term end.</t>
+          <t>Accrual artifact. Not a saving. Every one of the eight prepaid-released G&amp;A subscriptions is favorable by exactly 40.97 percent - the release is 59.03 percent of contracted ACV/12 on all eight, to five decimal places. One common factor, so one common cause: the prepaid amortization schedule is releasing below the contracted rate. The agreement (SWA-0064) is a 12-month term at USD 38,000 with 0 percent uplift and the sole 8050 posting for this vendor is the prepaid release, so ACV/12 is the correct monthly charge. Licenses active not seat-based. Under-release understates expense now and leaves a prepaid balance that will not extinguish at term end.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>8050 G&amp;A - software and tools / Notion Labs, Inc.</t>
+          <t>8050 G&amp;A - software and tools / Zoom Communications</t>
         </is>
       </c>
       <c r="C81" s="10" t="n">
-        <v>1058.47</v>
+        <v>0</v>
       </c>
       <c r="H81" s="36" t="inlineStr">
         <is>
-          <t>Accrual artifact. Not a saving. Every one of the eight prepaid-released G&amp;A subscriptions is favorable by exactly 40.97 percent - the release is 59.03 percent of contracted ACV/12 on all eight, to five decimal places. One common factor, so one common cause: the prepaid amortization schedule is releasing below the contracted rate. The agreement (SWA-0068) is a 12-month term at USD 31,000 with 0 percent uplift and the sole 8050 posting for this vendor is the prepaid release, so ACV/12 is the correct monthly charge. Licenses active 51 of 60. Under-release understates expense now and leaves a prepaid balance that will not extinguish at term end.</t>
+          <t>Accrual artifact. Not a saving. Every one of the eight prepaid-released G&amp;A subscriptions is favorable by exactly 40.97 percent - the release is 59.03 percent of contracted ACV/12 on all eight, to five decimal places. One common factor, so one common cause: the prepaid amortization schedule is releasing below the contracted rate. The agreement (SWA-0071) is a 12-month term at USD 34,000 with 0 percent uplift and the sole 8050 posting for this vendor is the prepaid release, so ACV/12 is the correct monthly charge. Licenses active 31 of 45. Under-release understates expense now and leaves a prepaid balance that will not extinguish at term end.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>8050 G&amp;A - software and tools / 1Password (AgileBits)</t>
+          <t>8050 G&amp;A - software and tools / Notion Labs, Inc.</t>
         </is>
       </c>
       <c r="C82" s="10" t="n">
-        <v>717.03</v>
+        <v>0</v>
       </c>
       <c r="H82" s="36" t="inlineStr">
         <is>
-          <t>Accrual artifact. Not a saving. Every one of the eight prepaid-released G&amp;A subscriptions is favorable by exactly 40.97 percent - the release is 59.03 percent of contracted ACV/12 on all eight, to five decimal places. One common factor, so one common cause: the prepaid amortization schedule is releasing below the contracted rate. The agreement (SWA-0066) is a 12-month term at USD 21,000 with 0 percent uplift and the sole 8050 posting for this vendor is the prepaid release, so ACV/12 is the correct monthly charge. Licenses active not seat-based. Under-release understates expense now and leaves a prepaid balance that will not extinguish at term end.</t>
+          <t>Accrual artifact. Not a saving. Every one of the eight prepaid-released G&amp;A subscriptions is favorable by exactly 40.97 percent - the release is 59.03 percent of contracted ACV/12 on all eight, to five decimal places. One common factor, so one common cause: the prepaid amortization schedule is releasing below the contracted rate. The agreement (SWA-0068) is a 12-month term at USD 31,000 with 0 percent uplift and the sole 8050 posting for this vendor is the prepaid release, so ACV/12 is the correct monthly charge. Licenses active 51 of 60. Under-release understates expense now and leaves a prepaid balance that will not extinguish at term end.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>7050 S&amp;M - events and conferences / Freeman, Goldcast, Informa</t>
+          <t>8050 G&amp;A - software and tools / 1Password (AgileBits)</t>
         </is>
       </c>
       <c r="C83" s="10" t="n">
-        <v>672</v>
+        <v>0</v>
       </c>
       <c r="H83" s="36" t="inlineStr">
         <is>
-          <t>Timing. Calendar-driven, not a trend. The plan itself ramps across Q1 (Jan USD 8,400, Feb USD 11,760, Mar USD 26,880) because the named event calendar puts the Q1 event in March. Trailing three-month average of USD 21,467 is inflated by Q4-2025 events; the trend file flags the line bumpy (CoV 0.83) and says so. January is on the calendar and on plan.</t>
+          <t>Accrual artifact. Not a saving. Every one of the eight prepaid-released G&amp;A subscriptions is favorable by exactly 40.97 percent - the release is 59.03 percent of contracted ACV/12 on all eight, to five decimal places. One common factor, so one common cause: the prepaid amortization schedule is releasing below the contracted rate. The agreement (SWA-0066) is a 12-month term at USD 21,000 with 0 percent uplift and the sole 8050 posting for this vendor is the prepaid release, so ACV/12 is the correct monthly charge. Licenses active not seat-based. Under-release understates expense now and leaves a prepaid balance that will not extinguish at term end.</t>
         </is>
       </c>
     </row>
@@ -8649,7 +8649,7 @@
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>614.6</v>
+        <v>0</v>
       </c>
       <c r="H84" s="36" t="inlineStr">
         <is>
